--- a/DOSSIES_MULTIFORMATO/FCECON/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FCECON/dossie.xlsx
@@ -636,12 +636,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022NE0001821</t>
+          <t>2022NE0001820</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6095.63</v>
+        <v>1854.05</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -659,19 +659,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2022NE0001820</t>
+          <t>2022NE0001821</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1854.05</v>
+        <v>6095.63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2017NE00960</t>
+          <t>2017NE00928</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2017NE00928</t>
+          <t>2017NE00960</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,10 +816,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE00989</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>2016NE00992</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>31/03/2016</t>
@@ -835,21 +839,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 664/2016 PARA CORREÇÃO DA DATA DE EMPENHO.</t>
+          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABAYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA - REF AO CONTRATO 13/2015 - VIGENCIA: 28/09/2015 A 28/09/2016 - COMPETENCIA: JAN E FEV/2016</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE00992</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2016NE00989</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>31/03/2016</t>
@@ -865,19 +865,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABAYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA - REF AO CONTRATO 13/2015 - VIGENCIA: 28/09/2015 A 28/09/2016 - COMPETENCIA: JAN E FEV/2016</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO N.º 664/2016 PARA CORREÇÃO DA DATA DE EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024NE0002734</t>
+          <t>2024NE0002728</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17313.21</v>
+        <v>15134</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -895,19 +895,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024NE0002733</t>
+          <t>2024NE0002736</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8332.629999999999</v>
+        <v>169.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -925,14 +925,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024NE0002730</t>
+          <t>2024NE0002731</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4504.15</v>
+        <v>5732.55</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024NE0002731</t>
+          <t>2024NE0002730</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5732.55</v>
+        <v>4504.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024NE0002736</t>
+          <t>2024NE0002733</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>169.33</v>
+        <v>8332.629999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1015,19 +1015,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024NE0002728</t>
+          <t>2024NE0002734</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15134</v>
+        <v>17313.21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1045,14 +1045,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023NE01043</t>
+          <t>2023NE0001043</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1075,19 +1075,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA PARA A PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SERVIDOR EM NUVEM, EM AMBIENTE DEDICADO.</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023NE01042</t>
+          <t>2023NE0001044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1105,19 +1105,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023NE01044</t>
+          <t>2023NE0001042</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1135,19 +1135,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO, DE FORMA DEDICADA, DE SERVIÇO DE ACESSO À INTERNET POR FIBRA ÓPTICA.</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023NE0001042</t>
+          <t>2023NE01044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1165,19 +1165,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO, DE FORMA DEDICADA, DE SERVIÇO DE ACESSO À INTERNET POR FIBRA ÓPTICA.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023NE0001044</t>
+          <t>2023NE01042</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023NE0001043</t>
+          <t>2023NE01043</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA PARA A PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SERVIDOR EM NUVEM, EM AMBIENTE DEDICADO.</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2014NE01013</t>
+          <t>2014NE01021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18/2011</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>528.35</v>
+        <v>34368.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Contrato No. 18/2011 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 14/2014</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2014NE01021</t>
+          <t>2014NE01013</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>18/2011</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34368.9</v>
+        <v>528.35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1345,19 +1345,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Contrato No. 14/2014</t>
+          <t>Contrato No. 18/2011 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025NE0001118</t>
+          <t>2025NE0001120</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025NE0001120</t>
+          <t>2025NE0001118</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025NE0003607</t>
+          <t>2025NE0003595</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4429.84</v>
+        <v>19559.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SERVIÇOS CONCERNENTES AO 2º TA CONTRATO 40/2020, VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA: 11/2023, DA SEGUINTE FORMA: FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - 25 MBPS - (1.000 X 1,90</t>
+          <t>SERVIÇOS DE HOSPEDAGEM DE SERVIDOR EM NUVEM, CONFORME O CONTRATO 21/2022, VIGÊNCIA: 01/09/2022 A 31/08/2023, COMPETÊNCIA 01/08/2023 A 31/08/2023, NOTAS FISCAIS Nºs 39400, 39401 e 39402 EMITIDAS EM 15/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025NE0003602</t>
+          <t>2025NE0003603</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5591.82</v>
+        <v>1749.68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SERVICO DE ACESSO GERENCIADO À REDE MUNDIAL DE 1 ATE 30 MBPS - (26.000 X 215.070). CONFORME 3º TA CONTRATO 40/2020 - VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA MÊS 08/2023 - FATURA Nº 143191 EMIT</t>
+          <t>SERVICO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - 25 MBPS - (1.000 X 1,906.790/ 30 X 7 DIAS), REFERENTE A 7 DIAS, E SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATÉ 30 MBPS - (26.000 X</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025NE0003608</t>
+          <t>2025NE0003599</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5591.82</v>
+        <v>14617.64</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1615,19 +1615,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATE 30 MBPS - (26.000 X 215.070). CONFORME 3º TA - CONTRATO Nº. 40/2020 VIGÊNCIA: 24/11/2023 A 23/11/2024, COMPETÊNCIA 12/2023. FATURA Nº 146173, EMITI</t>
+          <t>LICENCA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880) E HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - (2,058.00 X 2.570). R$ 5,289.06 POR GB EM DISCO MID - (2,058.00 X 1.280). R$ 2,634.24 ALOC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025NE0003600</t>
+          <t>2025NE0003612</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>22/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14617.64</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1645,19 +1645,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2º TA - CONTRATO Nº 21/2022 – REFERENTE A SERVIÇO DE LICENÇA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880), CONFORME NOTA FISCAL Nº 41458, NO VALOR DE R$ 321,76, EMITIDA EM 16/11/2023 E SERVICO: H</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025NE0003610</t>
+          <t>2025NE0003597</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2047.34</v>
+        <v>9779.700000000001</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SERVICO DE LICENCA DE USO DE SISTEMAS DE INFORMACAO, SISTEMA GESTOR DE CONTEUDO WEB LICENCA DE USO, GESTOR DE CONTEUDO WEB - (1.000 X 2,047.340) – REFERENTE AO 5º ADITIVO - CONTRATO Nº 18/2019 - COMPE</t>
+          <t>SERVICO DE HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - CONFORME NF 40556 DE 28/09/2023 – NO VALOR DE 9.129,34; SUPORTE TECNICO EM SISTEMAS DE INFORMACAO HORAS DE SUPORTE EM SISTEMAS DE INFORMACA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025NE0003598</t>
+          <t>2025NE0003596</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7308.82</v>
+        <v>477.71</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1705,19 +1705,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SERVICO DE LICENCA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880/ 30 X 15 DIAS ). R$ 160.88 E SERVIÇO DE HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - (2,058.00 X 2.570/ 30 X 15 DIAS ). R$ 2,64</t>
+          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/10/2023 A 07/10/2023, NOTA FISCAL Nº 41066 EMITIDA E</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025NE0003609</t>
+          <t>2025NE0003613</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>26/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2047.34</v>
+        <v>32062.7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1735,19 +1735,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SERVICO DE LICENCA DE USO DE SISTEMAS DE INFORMACAO, SISTEMA GESTOR DE CONTEUDO WEB LICENCA DE USO, GESTOR DE CONTEUDO WEB - (1.000 X 2,047.340) – REFERENTE AO 5º ADITIVO - CONTRATO Nº 18/2019 - COMPE</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025NE0003611</t>
+          <t>2025NE0003601</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1692.39</v>
+        <v>1906.79</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1765,28 +1765,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SALDO RESTANTE DA NF 33913 DE 01/12/2022- REFERENTE AO SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - COMPETÊNCIA: DEZEMBRO/2022. CONFORME 2º TERMO ADITIVO DO CONTRATO 40/2020, VIGÊNCIA</t>
+          <t>SERVICO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS - 25 MBPS - (1.000 X 1,906.790). CONFORME 3º TA CONTRATO 40/2020 - VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA MÊS 08/2023 - NF Nº 39399</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025NE0003604</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>40/2020</t>
-        </is>
-      </c>
+          <t>2025NE0003650</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>29/10/2025</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5484.47</v>
+        <v>117937.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1795,24 +1791,28 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATE 30 MBPS - (18.000 X 198.760) E FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS CIRCUITO DE TRANSMISSAO DE DADOS - 25 MBPS - (1.000 X 1,906.790). C</t>
+          <t>139006 - LICENÇA DE SOFTWARE, Aquisição de licença (36 meses) de software antivírus Kaspersky com suporte e atualizações por 36 meses; 139009 - CAPACITAÇÃO PROFISSIONAL; 14800 - SERVIÇOS DE INFORMÁTIC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025NE0003650</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2025NE0003604</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>40/2020</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>29/10/2025</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>117937.3</v>
+        <v>5484.47</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1821,19 +1821,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>139006 - LICENÇA DE SOFTWARE, Aquisição de licença (36 meses) de software antivírus Kaspersky com suporte e atualizações por 36 meses; 139009 - CAPACITAÇÃO PROFISSIONAL; 14800 - SERVIÇOS DE INFORMÁTIC</t>
+          <t>SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATE 30 MBPS - (18.000 X 198.760) E FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS CIRCUITO DE TRANSMISSAO DE DADOS - 25 MBPS - (1.000 X 1,906.790). C</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025NE0003601</t>
+          <t>2025NE0003611</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1906.79</v>
+        <v>1692.39</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SERVICO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSAO DE DADOS - 25 MBPS - (1.000 X 1,906.790). CONFORME 3º TA CONTRATO 40/2020 - VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA MÊS 08/2023 - NF Nº 39399</t>
+          <t>SALDO RESTANTE DA NF 33913 DE 01/12/2022- REFERENTE AO SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - COMPETÊNCIA: DEZEMBRO/2022. CONFORME 2º TERMO ADITIVO DO CONTRATO 40/2020, VIGÊNCIA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025NE0003613</t>
+          <t>2025NE0003609</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>26/2025</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32062.7</v>
+        <v>2047.34</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
+          <t>SERVICO DE LICENCA DE USO DE SISTEMAS DE INFORMACAO, SISTEMA GESTOR DE CONTEUDO WEB LICENCA DE USO, GESTOR DE CONTEUDO WEB - (1.000 X 2,047.340) – REFERENTE AO 5º ADITIVO - CONTRATO Nº 18/2019 - COMPE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025NE0003596</t>
+          <t>2025NE0003598</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>477.71</v>
+        <v>7308.82</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/10/2023 A 07/10/2023, NOTA FISCAL Nº 41066 EMITIDA E</t>
+          <t>SERVICO DE LICENCA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880/ 30 X 15 DIAS ). R$ 160.88 E SERVIÇO DE HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - (2,058.00 X 2.570/ 30 X 15 DIAS ). R$ 2,64</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025NE0003597</t>
+          <t>2025NE0003610</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9779.700000000001</v>
+        <v>2047.34</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1941,19 +1941,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SERVICO DE HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - CONFORME NF 40556 DE 28/09/2023 – NO VALOR DE 9.129,34; SUPORTE TECNICO EM SISTEMAS DE INFORMACAO HORAS DE SUPORTE EM SISTEMAS DE INFORMACA</t>
+          <t>SERVICO DE LICENCA DE USO DE SISTEMAS DE INFORMACAO, SISTEMA GESTOR DE CONTEUDO WEB LICENCA DE USO, GESTOR DE CONTEUDO WEB - (1.000 X 2,047.340) – REFERENTE AO 5º ADITIVO - CONTRATO Nº 18/2019 - COMPE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025NE0003612</t>
+          <t>2025NE0003600</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22/2025</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>14617.64</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1971,19 +1971,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
+          <t>2º TA - CONTRATO Nº 21/2022 – REFERENTE A SERVIÇO DE LICENÇA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880), CONFORME NOTA FISCAL Nº 41458, NO VALOR DE R$ 321,76, EMITIDA EM 16/11/2023 E SERVICO: H</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025NE0003599</t>
+          <t>2025NE0003608</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14617.64</v>
+        <v>5591.82</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2001,14 +2001,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LICENCA DE USO DE VPN POR CONEXAO VPN - (2.000 X 160.880) E HOSPEDAGEM DE SERVIDORES POR GB EM DISCO BACKUP - (2,058.00 X 2.570). R$ 5,289.06 POR GB EM DISCO MID - (2,058.00 X 1.280). R$ 2,634.24 ALOC</t>
+          <t>SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATE 30 MBPS - (26.000 X 215.070). CONFORME 3º TA - CONTRATO Nº. 40/2020 VIGÊNCIA: 24/11/2023 A 23/11/2024, COMPETÊNCIA 12/2023. FATURA Nº 146173, EMITI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025NE0003603</t>
+          <t>2025NE0003602</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1749.68</v>
+        <v>5591.82</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2031,19 +2031,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SERVICO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - 25 MBPS - (1.000 X 1,906.790/ 30 X 7 DIAS), REFERENTE A 7 DIAS, E SERVICO DE ACESSO GERENCIADO A REDE MUNDIAL DE 1 ATÉ 30 MBPS - (26.000 X</t>
+          <t>SERVICO DE ACESSO GERENCIADO À REDE MUNDIAL DE 1 ATE 30 MBPS - (26.000 X 215.070). CONFORME 3º TA CONTRATO 40/2020 - VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA MÊS 08/2023 - FATURA Nº 143191 EMIT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025NE0003595</t>
+          <t>2025NE0003607</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>19559.4</v>
+        <v>4429.84</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE HOSPEDAGEM DE SERVIDOR EM NUVEM, CONFORME O CONTRATO 21/2022, VIGÊNCIA: 01/09/2022 A 31/08/2023, COMPETÊNCIA 01/08/2023 A 31/08/2023, NOTAS FISCAIS Nºs 39400, 39401 e 39402 EMITIDAS EM 15/</t>
+          <t>SERVIÇOS CONCERNENTES AO 2º TA CONTRATO 40/2020, VIGÊNCIA: 24/11/2022 A 23/11/2023 - COMPETÊNCIA: 11/2023, DA SEGUINTE FORMA: FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - 25 MBPS - (1.000 X 1,90</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023NE0002542</t>
+          <t>2023NE0002543</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>136.78</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2199,14 +2199,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO AO CONTRATO Nº 040/2020 - 01/06/2023 - 31/07/2023 - 2023NE0000698]</t>
+          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 5º ADITIVO AO CONTRATO Nº 018/2019 - 01/10/2023 - 31/10/2023 - 2023NE0001709]</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023NE0002543</t>
+          <t>2023NE0002542</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>68.23999999999999</v>
+        <v>136.78</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 5º ADITIVO AO CONTRATO Nº 018/2019 - 01/10/2023 - 31/10/2023 - 2023NE0001709]</t>
+          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO AO CONTRATO Nº 040/2020 - 01/06/2023 - 31/07/2023 - 2023NE0000698]</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2022NE0000565</t>
+          <t>2022NE0000566</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>664.99</v>
+        <v>6071.67</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2341,19 +2341,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022NE0000566</t>
+          <t>2022NE0000565</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6071.67</v>
+        <v>664.99</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024NE0000640</t>
+          <t>2024NE0000641</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/08/2023 A 31/08/2023, NOTA FISCAL Nº 39398 EMITIDA E</t>
+          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/09/2023 A 30/09/2023, NOTA FISCAL Nº 40554 EMITIDA E</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024NE0000641</t>
+          <t>2024NE0000640</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2521,19 +2521,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/09/2023 A 30/09/2023, NOTA FISCAL Nº 40554 EMITIDA E</t>
+          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 4º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2022 A 07/10/2023, COMPETÊNCIA 01/08/2023 A 31/08/2023, NOTA FISCAL Nº 39398 EMITIDA E</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2022NE0000070</t>
+          <t>2022NE0000071</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1994.97</v>
+        <v>18215.01</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2551,19 +2551,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2022NE0000071</t>
+          <t>2022NE0000070</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18215.01</v>
+        <v>1994.97</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,14 +2581,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025NE0003852</t>
+          <t>2025NE0003851</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2618,12 +2618,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025NE0003848</t>
+          <t>2025NE0003860</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1700.79</v>
+        <v>6071.65</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,19 +2641,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 1º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2020 ATÉ 07/10/2021, COMPETÊNCIA 01 A 31/12/2020, NFSe Nº 18186 EMITIDA E</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025NE0003847</t>
+          <t>2025NE0003864</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>396.85</v>
+        <v>6071.65</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 1º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2020 ATÉ 07/10/2021, COMPETÊNCIA 01 A 07/10/2021, NFSe Nº 24413 EMITIDA E</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA SERVIÇO DE ACESSO Á INTERNET TC:13/2015 AD:02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025NE0003855</t>
+          <t>2025NE0003844</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>663.66</v>
+        <v>7093.14</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2701,19 +2701,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME 1º TERMO ADITIVO AO CONTRATO 40/2020, VIGÊNCIA: 24/11/2021 ATÉ 23/11/2022, COMPETÊNCIA DEZEMBRO DE 2021, NFSe Nº 25776 e 25777 EM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025NE0003856</t>
+          <t>2025NE0003863</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>664.99</v>
+        <v>12130</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025NE0003843</t>
+          <t>2025NE0003859</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1692.39</v>
+        <v>6071.65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2761,19 +2761,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SALDO RESTANTE DA NF 33913 DE 01/12/2022- REFERENTE AO SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - COMPETÊNCIA: DEZEMBRO/2022. CONFORME 2º TERMO ADITIVO DO CONTRATO 40/2020, VIGÊNCIA</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025NE0003850</t>
+          <t>2025NE0003858</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>664.99</v>
+        <v>5464.49</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2791,14 +2791,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025NE0003846</t>
+          <t>2025NE0003845</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4462.68</v>
+        <v>5438.07</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2821,14 +2821,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME CONTRATO 40/2020, VIGÊNCIA: 24/11/2020 ATÉ 23/11/2021, COMPETÊNCIA OUTUBRO DE 2021, NFSe Nº 24414 EMITIDA EM 15/10/2021, VALOR TO</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME CONTRATO 40/2020, VIGÊNCIA: 24/11/2020 ATÉ 23/11/2021, COMPETÊNCIA NOVEMBRO DE 2021, NFSe Nº 25202 e 25203 EMITIDAS EM 17/11/2021</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025NE0003866</t>
+          <t>2025NE0003857</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2531.6</v>
+        <v>663.66</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025NE0003854</t>
+          <t>2025NE0003853</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2888,7 +2888,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025NE0003865</t>
+          <t>2025NE0003862</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 02.</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025NE0003867</t>
+          <t>2025NE0003861</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>438.2</v>
+        <v>6071.65</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2941,19 +2941,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOSSERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE 4º TERMO ADITIVO AO CONTRATO Nº 018/2019.</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025NE0003861</t>
+          <t>2025NE0003867</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6071.65</v>
+        <v>438.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2971,14 +2971,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOSSERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE 4º TERMO ADITIVO AO CONTRATO Nº 018/2019.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025NE0003862</t>
+          <t>2025NE0003865</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3001,14 +3001,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025NE0003853</t>
+          <t>2025NE0003854</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025NE0003857</t>
+          <t>2025NE0003866</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>663.66</v>
+        <v>2531.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3061,14 +3061,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025NE0003845</t>
+          <t>2025NE0003846</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5438.07</v>
+        <v>4462.68</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3091,19 +3091,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME CONTRATO 40/2020, VIGÊNCIA: 24/11/2020 ATÉ 23/11/2021, COMPETÊNCIA NOVEMBRO DE 2021, NFSe Nº 25202 e 25203 EMITIDAS EM 17/11/2021</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME CONTRATO 40/2020, VIGÊNCIA: 24/11/2020 ATÉ 23/11/2021, COMPETÊNCIA OUTUBRO DE 2021, NFSe Nº 24414 EMITIDA EM 15/10/2021, VALOR TO</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025NE0003858</t>
+          <t>2025NE0003850</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5464.49</v>
+        <v>664.99</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3121,19 +3121,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025NE0003859</t>
+          <t>2025NE0003843</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6071.65</v>
+        <v>1692.39</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3151,19 +3151,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
+          <t>SALDO RESTANTE DA NF 33913 DE 01/12/2022- REFERENTE AO SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS - COMPETÊNCIA: DEZEMBRO/2022. CONFORME 2º TERMO ADITIVO DO CONTRATO 40/2020, VIGÊNCIA</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025NE0003863</t>
+          <t>2025NE0003856</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12130</v>
+        <v>664.99</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3181,19 +3181,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025NE0003844</t>
+          <t>2025NE0003855</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7093.14</v>
+        <v>663.66</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3211,19 +3211,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE UM LINK DE INTERNET, CONFORME 1º TERMO ADITIVO AO CONTRATO 40/2020, VIGÊNCIA: 24/11/2021 ATÉ 23/11/2022, COMPETÊNCIA DEZEMBRO DE 2021, NFSe Nº 25776 e 25777 EM</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE TC: 14/2014 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025NE0003864</t>
+          <t>2025NE0003847</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6071.65</v>
+        <v>396.85</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3241,19 +3241,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA SERVIÇO DE ACESSO Á INTERNET TC:13/2015 AD:02</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 1º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2020 ATÉ 07/10/2021, COMPETÊNCIA 01 A 07/10/2021, NFSe Nº 24413 EMITIDA E</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025NE0003860</t>
+          <t>2025NE0003848</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6071.65</v>
+        <v>1700.79</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3271,14 +3271,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO À INTERNET TC: 13/2015 AD: 03.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE, CONFORME 1º TERMO ADITIVO AO CONTRATO 18/2019, VIGÊNCIA: 08/10/2020 ATÉ 07/10/2021, COMPETÊNCIA 01 A 31/12/2020, NFSe Nº 18186 EMITIDA E</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025NE0003851</t>
+          <t>2025NE0003852</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3308,12 +3308,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2019NE01672</t>
+          <t>2019NE01671</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6071.65</v>
+        <v>66.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3331,19 +3331,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2018 A 28/09/20</t>
+          <t>OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON. VIGÊNCIA: 04/06/2018 A 04/06/2019. VALOR GLOBAL: R$ 7.979,88 VALOR MENSAL: R$ 664,99.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2019NE01671</t>
+          <t>2019NE01672</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>66.5</v>
+        <v>6071.65</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3361,14 +3361,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON. VIGÊNCIA: 04/06/2018 A 04/06/2019. VALOR GLOBAL: R$ 7.979,88 VALOR MENSAL: R$ 664,99.</t>
+          <t>3º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2018 A 28/09/20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025NE0001844</t>
+          <t>2025NE01844</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3391,14 +3391,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>Contrato 018/2023 Aditivo nº 01 - Serviços de Hospedagem em Infraestrutura Virtualizada.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025NE01844</t>
+          <t>2025NE0001844</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Contrato 018/2023 Aditivo nº 01 - Serviços de Hospedagem em Infraestrutura Virtualizada.</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -3578,14 +3578,10 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2023NE01282</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>18/2019</t>
-        </is>
-      </c>
+          <t>2023NE0001282</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>25/07/2023</t>
@@ -3601,17 +3597,21 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4º TA do Contrato 018/2019 - Serviços Especializados em Reformulação e Atualização de Web Site. Obs.: Valor Empenhado refere-se ao restante das parcelas de janeiro a maio (R$ 169,33 mês e a parcial da</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2023NE0001282</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>2023NE01282</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>18/2019</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>25/07/2023</t>
@@ -3627,24 +3627,28 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>4º TA do Contrato 018/2019 - Serviços Especializados em Reformulação e Atualização de Web Site. Obs.: Valor Empenhado refere-se ao restante das parcelas de janeiro a maio (R$ 169,33 mês e a parcial da</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2016NE01755</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2016NE01760</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>25/05/2016</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>197.26</v>
+        <v>789.03</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3653,28 +3657,24 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 1374/2016. MOTIVO: EQUIVOCO NO PROCESSO</t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014 OBJETO DO ADITIVO: APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DEST</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2016NE01760</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2016NE01755</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>25/05/2016</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>789.03</v>
+        <v>197.26</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014 OBJETO DO ADITIVO: APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DEST</t>
+          <t>ANULAÇÃO TOTAL DA NE 1374/2016. MOTIVO: EQUIVOCO NO PROCESSO</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024NE0001083</t>
+          <t>2024NE0001082</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3803,19 +3803,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024NE0001082</t>
+          <t>2024NE0001083</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3960,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2022NE0000762</t>
+          <t>2022NE0000761</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6071.67</v>
+        <v>664.99</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3983,19 +3983,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2022NE0000761</t>
+          <t>2022NE0000762</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>664.99</v>
+        <v>6071.67</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2023NE0000219</t>
+          <t>2023NE0000217</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2023NE0000217</t>
+          <t>2023NE0000219</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024NE0002631</t>
+          <t>2024NE0002628</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1878.01</v>
+        <v>2334.22</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2024NE0002630</t>
+          <t>2024NE0002629</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>7567</v>
+        <v>17225.18</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4249,19 +4249,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024NE0002629</t>
+          <t>2024NE0002630</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>17225.18</v>
+        <v>7567</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4279,19 +4279,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2024NE0002628</t>
+          <t>2024NE0002631</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2334.22</v>
+        <v>1878.01</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4309,19 +4309,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2023NE0001630</t>
+          <t>2023NE0001632</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2023NE0001632</t>
+          <t>2023NE0001630</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2015NE01121</t>
+          <t>2015NE01123</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>REF. RESSARCIMENTO DE DESPESA COM CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SITE, CONF. MEMO 123/2015 DA GEOFI/FCECON DE ACORDO COM O PARECER Nº 62/2015-FCECON, DATADO DE 18/06</t>
+          <t>ANULAÇÃO TOTAL DA NE 1121/2015. MOTIVO: EQUIVOCO NO VALOR</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2015NE01123</t>
+          <t>2015NE01121</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4489,19 +4489,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 1121/2015. MOTIVO: EQUIVOCO NO VALOR</t>
+          <t>REF. RESSARCIMENTO DE DESPESA COM CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SITE, CONF. MEMO 123/2015 DA GEOFI/FCECON DE ACORDO COM O PARECER Nº 62/2015-FCECON, DATADO DE 18/06</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025NE0001440</t>
+          <t>2025NE0001439</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>19559.4</v>
+        <v>1878.01</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4519,19 +4519,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025NE0001439</t>
+          <t>2025NE0001440</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1878.01</v>
+        <v>19559.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026NE0000022</t>
+          <t>2026NE0000023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>19559.4</v>
+        <v>7567</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026NE0000023</t>
+          <t>2026NE0000022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7567</v>
+        <v>19559.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4664,12 +4664,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026NE0000013</t>
+          <t>2026NE0000012</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>26/2025</t>
+          <t>25/2025</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026NE0000012</t>
+          <t>2026NE0000013</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>25/2025</t>
+          <t>26/2025</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024NE0000525</t>
+          <t>2024NE0000524</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4837,19 +4837,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2024NE0000524</t>
+          <t>2024NE0000525</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020NE01914</t>
+          <t>2020NE01915</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
+          <t xml:space="preserve">contratação de pessoa jurídica para prestação de serviços especializados em manutenção e suporte de reformulação do site da FCECON, melhorando o gerenciamento de conteúdo, tornando as atualizações de </t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020NE01915</t>
+          <t>2020NE01914</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">contratação de pessoa jurídica para prestação de serviços especializados em manutenção e suporte de reformulação do site da FCECON, melhorando o gerenciamento de conteúdo, tornando as atualizações de </t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021NE0000596</t>
+          <t>2021NE0000595</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>7093.14</v>
+        <v>664.99</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5043,19 +5043,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>contratação de pessoa jurídica especializada para prestação de serviços de telecomunicações, objetivando a implantação, configuração e manutenção de acesso à Rede Internet, por intermédio de 1 link de</t>
+          <t xml:space="preserve">contratação de pessoa jurídica para prestação de serviços especializados em manutenção e suporte de reformulação do site da FCECON, melhorando o gerenciamento de conteúdo, tornando as atualizações de </t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021NE0000595</t>
+          <t>2021NE0000596</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>664.99</v>
+        <v>7093.14</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5073,19 +5073,19 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">contratação de pessoa jurídica para prestação de serviços especializados em manutenção e suporte de reformulação do site da FCECON, melhorando o gerenciamento de conteúdo, tornando as atualizações de </t>
+          <t>contratação de pessoa jurídica especializada para prestação de serviços de telecomunicações, objetivando a implantação, configuração e manutenção de acesso à Rede Internet, por intermédio de 1 link de</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2017NE02216</t>
+          <t>2017NE02098</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5458.5</v>
+        <v>1327.32</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
+          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2017NE02217</t>
+          <t>2017NE02144</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>18214.95</v>
+        <v>6065</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5133,28 +5133,24 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR O REAJUSTE DE 0,11% SOBRE O VALOR DO CONTRATO. OBJETO DO CONTRATO: FORNECIMENTO DE </t>
+          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2017NE02101</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2017NE02143</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1990.98</v>
+        <v>6065</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
+          <t>ANULAÇÃO TOTAL DA NE2125/17 PARA CORREÇÃO DO FUNDAMENTO LEGAL.</t>
         </is>
       </c>
     </row>
@@ -5200,17 +5196,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2017NE02143</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>2017NE02101</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6065</v>
+        <v>1990.98</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE2125/17 PARA CORREÇÃO DO FUNDAMENTO LEGAL.</t>
+          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2017NE02144</t>
+          <t>2017NE02217</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6065</v>
+        <v>18214.95</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5249,19 +5249,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
+          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR O REAJUSTE DE 0,11% SOBRE O VALOR DO CONTRATO. OBJETO DO CONTRATO: FORNECIMENTO DE </t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2017NE02098</t>
+          <t>2017NE02216</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1327.32</v>
+        <v>5458.5</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
+          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2020NE01390</t>
+          <t>2020NE01391</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1624.16</v>
+        <v>76.63</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE CT. 18/2019 PARCIAL DA PARCELA DE FEVEREIRO/2020</t>
+          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE CT. 18/2019 RESTANTE DA PARCELA DE FEVEREIRO/2020</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2020NE01391</t>
+          <t>2020NE01390</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>76.63</v>
+        <v>1624.16</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5395,21 +5395,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE CT. 18/2019 RESTANTE DA PARCELA DE FEVEREIRO/2020</t>
+          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE CT. 18/2019 PARCIAL DA PARCELA DE FEVEREIRO/2020</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2017NE00821</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2017NE00825</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>18/05/2017</t>
@@ -5425,19 +5421,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
+          <t>ANULAÇÃO TOTAL DA NE 821. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2017NE00827</t>
+          <t>2017NE00828</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5446,7 +5442,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1265.8</v>
+        <v>12130</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5455,17 +5451,21 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
+          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2017NE00826</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+          <t>2017NE00820</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr">
         <is>
           <t>18/05/2017</t>
@@ -5481,21 +5481,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 820. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
+          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2017NE00820</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2017NE00826</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>18/05/2017</t>
@@ -5511,19 +5507,19 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
+          <t>ANULAÇÃO TOTAL DA NE 820. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2017NE00828</t>
+          <t>2017NE00827</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5532,7 +5528,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>12130</v>
+        <v>1265.8</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5541,17 +5537,21 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
+          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2017NE00825</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>2017NE00821</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr">
         <is>
           <t>18/05/2017</t>
@@ -5567,14 +5567,14 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 821. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
+          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2024NE0003005</t>
+          <t>2024NE0003004</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>12658.35</v>
+        <v>17323.97</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5597,14 +5597,14 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2024NE0003004</t>
+          <t>2024NE0003005</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>17323.97</v>
+        <v>12658.35</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5627,19 +5627,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2016NE02957</t>
+          <t>2016NE02959</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>18195</v>
+        <v>1265.8</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5657,19 +5657,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO N.º 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/0</t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2016NE02959</t>
+          <t>2016NE02957</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1265.8</v>
+        <v>18195</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5687,19 +5687,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
+          <t>1º TERMO ADITIVO AO CONTRATO N.º 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2016NE02957</t>
+          <t>2016NE02959</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>18195</v>
+        <v>1265.8</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5717,19 +5717,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO N.º 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/0</t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2016NE02959</t>
+          <t>2016NE02957</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1265.8</v>
+        <v>18195</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
+          <t>1º TERMO ADITIVO AO CONTRATO N.º 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/0</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2023NE0000699</t>
+          <t>2023NE00699</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5807,19 +5807,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>4º Aditivo do Contrato 018/2019 - Prestação de Serviço em Manutenção e Suporte de Reformulação do site.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2023NE0000698</t>
+          <t>2023NE0000697</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>15134</v>
+        <v>39118.8</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5837,19 +5837,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2023NE0000697</t>
+          <t>2023NE0000698</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>39118.8</v>
+        <v>15134</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5867,14 +5867,14 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2023NE00699</t>
+          <t>2023NE0000699</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5897,14 +5897,14 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>4º Aditivo do Contrato 018/2019 - Prestação de Serviço em Manutenção e Suporte de Reformulação do site.</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2020NE02156</t>
+          <t>2020NE02159</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5934,17 +5934,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2020NE02157</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
+          <t>2020NE02155</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>18/2019</t>
+        </is>
+      </c>
       <c r="C181" t="inlineStr">
         <is>
           <t>16/11/2020</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1700.79</v>
+        <v>1189.06</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5953,28 +5957,24 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DEVIDO ASSINATURA TER OCORRIDO ANTES DA DESCRIÇÃO.</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2020NE02155</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>18/2019</t>
-        </is>
-      </c>
+          <t>2020NE02157</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>16/11/2020</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1189.06</v>
+        <v>1700.79</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
+          <t>ANULAÇÃO TOTAL DEVIDO ASSINATURA TER OCORRIDO ANTES DA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2020NE02159</t>
+          <t>2020NE02156</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2023NE0001380</t>
+          <t>2023NE0001379</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>21/2022</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>39118.8</v>
+        <v>15134</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6073,19 +6073,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2023NE0001379</t>
+          <t>2023NE0001380</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>21/2022</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>15134</v>
+        <v>39118.8</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE PESSOA JURIDICA para Prestação de Serviços de Hospedagem de servidor em nuvem, em ambiente dedicado, para comportar os sistemas da CONTRATANTE no ambiente de produção do Data Center da </t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2015NE00834</t>
+          <t>2015NE00663</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6163,14 +6163,14 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: EQUIVOCO NA DATA DE EMISSÃO.</t>
+          <t>REF. AO 3º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2014 A 12/04/2015 NO VALOR MENSAL R$ 528,35 E VALOR GLOBAL DE R$ 6.340,20</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2015NE00663</t>
+          <t>2015NE00834</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>REF. AO 3º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2014 A 12/04/2015 NO VALOR MENSAL R$ 528,35 E VALOR GLOBAL DE R$ 6.340,20</t>
+          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: EQUIVOCO NA DATA DE EMISSÃO.</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2023NE0001556</t>
+          <t>2023NE0001557</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO DO CONTRATO Nº 040/2020 - 01/01/2023 - 28/02/2023 - 2023NE0000039]</t>
+          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO DO CONTRATO Nº 040/2020 - 01/03/2023 - 30/04/2023 - 2023NE0000698]</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2023NE0001557</t>
+          <t>2023NE0001556</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO DO CONTRATO Nº 040/2020 - 01/03/2023 - 30/04/2023 - 2023NE0000698]</t>
+          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 2º ADITIVO DO CONTRATO Nº 040/2020 - 01/01/2023 - 28/02/2023 - 2023NE0000039]</t>
         </is>
       </c>
     </row>
@@ -6338,21 +6338,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2024NE0001173</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>40/2020</t>
-        </is>
-      </c>
+          <t>2024NE0001183</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>14/06/2024</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7567</v>
+        <v>338.66</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6361,24 +6357,28 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 3º ADITIVO AO CONTRATO Nº 040/2020 - COMPETÊNCIA: 01/02/2024 A 28/02/2024 - 2024NE0000007]</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2024NE0001183</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>2024NE0001173</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>40/2020</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>14/06/2024</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>338.66</v>
+        <v>7567</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6387,28 +6387,24 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: ECONOMIA ORÇAMENTÁRIA DO 3º ADITIVO AO CONTRATO Nº 040/2020 - COMPETÊNCIA: 01/02/2024 A 28/02/2024 - 2024NE0000007]</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2016NE01289</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2016NE01392</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>14/04/2016</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1890.26</v>
+        <v>632.9</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6417,19 +6413,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1º T.A. CONT. N.º 013/2015 - FORNECIMENTO DE LINK DE INTERNET - VIGÊNCIA: 20/04/2016 a 28/09/2016 - VALOR EMPENHADO REF. A COMPETÊNCIA DO MÊS DE ABRIL DE 2016.</t>
+          <t>ANULAÇÃO PARCIAL DA NE 663/2016. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2016NE01394</t>
+          <t>2016NE01359</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6438,7 +6434,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1033.74</v>
+        <v>1890.26</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6447,19 +6443,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REFORÇO DA NOTA DE EMPENHO N.º 663/2016 - REFERENTE AO 2º T.A. CONT. N.º 14/2014 - REFERENTE A COMPETÊNCIA DE MARÇO E ABRIL DE 2016</t>
+          <t>1º T.A. CONT. N.º 013/2015 - FORNECIMENTO DE 01 (UM) LINK DE INTERNET - VIGÊNCIA: 28/09/2016 a 28/09/2016 - VALOR EMPENHADO REF. AO PERIODO DE 20 a 30 DE ABR. DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2016NE01373</t>
+          <t>2016NE01357</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6468,7 +6464,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>400.84</v>
+        <v>3841.17</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6477,24 +6473,28 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE N.º 663/2014- REF. AO 1º T.A. CONT. N.º 14/2014 - VIGENCIA: 04/06/2015 a 04/06/2016 - VALOR EMPENHADO REF. AO MES DE ABRIL (PARCIAL) DE 2016.</t>
+          <t>REFORÇO DA NOTA DE EMPENHO N.º 992/2016 PARA ATENDER O CONTRATO N.º 013/2015 - VIGÊNCIA: 28/09/2015 a 28/09/2016 - VALOR EMPENHADO REF. AO MES DE ABRIL (PARCIAL) DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2016NE01371</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
+          <t>2016NE01374</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
           <t>14/04/2016</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>139.97</v>
+        <v>197.26</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6503,14 +6503,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>ANULÇÃO TOTAL DA NOTA DE EMPENHO N.º 1158/2016 - EMPENHADO ENDEVIDO.</t>
+          <t>2º T.A. CONT. N.º 014/2014 - APLICAÇÃO DE SUPRESSÃO NO VALOR INICIAL DO CONTRATO - VIGÊNCIA: 04/06/2015 a 04/06/2016 - VALOR EMPENHADO REF. AO MÊS DE ABRIL DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2016NE01372</t>
+          <t>2016NE01393</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>241.77</v>
+        <v>400.84</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ANULÇÃO TOTAL DA NOTA DE EMPENHO N.º 1183/2016 - EMPENHADO ENDEVIDO.</t>
+          <t>ANULAÇÃO PARCIAL DA NE 663/2016. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2016NE01393</t>
+          <t>2016NE01372</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>400.84</v>
+        <v>241.77</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6581,28 +6581,24 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 663/2016. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>ANULÇÃO TOTAL DA NOTA DE EMPENHO N.º 1183/2016 - EMPENHADO ENDEVIDO.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2016NE01374</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2016NE01371</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
           <t>14/04/2016</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>197.26</v>
+        <v>139.97</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6611,19 +6607,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2º T.A. CONT. N.º 014/2014 - APLICAÇÃO DE SUPRESSÃO NO VALOR INICIAL DO CONTRATO - VIGÊNCIA: 04/06/2015 a 04/06/2016 - VALOR EMPENHADO REF. AO MÊS DE ABRIL DE 2016.</t>
+          <t>ANULÇÃO TOTAL DA NOTA DE EMPENHO N.º 1158/2016 - EMPENHADO ENDEVIDO.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2016NE01357</t>
+          <t>2016NE01373</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6632,7 +6628,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>3841.17</v>
+        <v>400.84</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6641,19 +6637,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>REFORÇO DA NOTA DE EMPENHO N.º 992/2016 PARA ATENDER O CONTRATO N.º 013/2015 - VIGÊNCIA: 28/09/2015 a 28/09/2016 - VALOR EMPENHADO REF. AO MES DE ABRIL (PARCIAL) DE 2016.</t>
+          <t>REFORÇO DA NE N.º 663/2014- REF. AO 1º T.A. CONT. N.º 14/2014 - VIGENCIA: 04/06/2015 a 04/06/2016 - VALOR EMPENHADO REF. AO MES DE ABRIL (PARCIAL) DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2016NE01359</t>
+          <t>2016NE01394</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6662,7 +6658,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1890.26</v>
+        <v>1033.74</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6671,24 +6667,28 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>1º T.A. CONT. N.º 013/2015 - FORNECIMENTO DE 01 (UM) LINK DE INTERNET - VIGÊNCIA: 28/09/2016 a 28/09/2016 - VALOR EMPENHADO REF. AO PERIODO DE 20 a 30 DE ABR. DE 2016.</t>
+          <t>REFORÇO DA NOTA DE EMPENHO N.º 663/2016 - REFERENTE AO 2º T.A. CONT. N.º 14/2014 - REFERENTE A COMPETÊNCIA DE MARÇO E ABRIL DE 2016</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2016NE01392</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>2016NE01289</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>14/04/2016</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>632.9</v>
+        <v>1890.26</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 663/2016. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>1º T.A. CONT. N.º 013/2015 - FORNECIMENTO DE LINK DE INTERNET - VIGÊNCIA: 20/04/2016 a 28/09/2016 - VALOR EMPENHADO REF. A COMPETÊNCIA DO MÊS DE ABRIL DE 2016.</t>
         </is>
       </c>
     </row>
@@ -6764,21 +6764,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2024NE0002956</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>18/2023</t>
-        </is>
-      </c>
+          <t>2024NE0002952</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
           <t>13/12/2024</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>58678.2</v>
+        <v>17313.21</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6787,24 +6783,28 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
+          <t>ANULAÇÃO PARA AJUSTE NO PB</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2024NE0002952</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
+          <t>2024NE0002956</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>18/2023</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr">
         <is>
           <t>13/12/2024</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>17313.21</v>
+        <v>58678.2</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA AJUSTE NO PB</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA,</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2016NE02934</t>
+          <t>2016NE02935</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>928.25</v>
+        <v>3101.21</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6873,24 +6873,28 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 30/06/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO.</t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2016NE02936</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
+          <t>2016NE02935</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
           <t>13/10/2016</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>789.03</v>
+        <v>3101.21</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6899,28 +6903,24 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 1760. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2016NE02934</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2016NE02936</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
           <t>13/10/2016</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>928.25</v>
+        <v>789.03</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6929,24 +6929,28 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 30/06/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO.</t>
+          <t>ANULAÇÃO TOTAL DA NE 1760. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2016NE02936</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
+          <t>2016NE02934</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C216" t="inlineStr">
         <is>
           <t>13/10/2016</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>789.03</v>
+        <v>928.25</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6955,28 +6959,24 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 1760. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>1º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 30/06/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2016NE02935</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2016NE02936</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
           <t>13/10/2016</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3101.21</v>
+        <v>789.03</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6985,14 +6985,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
+          <t>ANULAÇÃO TOTAL DA NE 1760. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2016NE02935</t>
+          <t>2016NE02934</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7006,7 +7006,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>3101.21</v>
+        <v>928.25</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 06/05/2016. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPL</t>
+          <t>1º TERMO ADITIVO AO CONTRATO N.º 014/2014, EXTR. PUBL. NO D.O. DE 30/06/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAR SUPRESSÃO DE 15% NO VALOR TOTAL DO CONTRATO.</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2022NE0002310</t>
+          <t>2022NE0002312</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10244.16</v>
+        <v>5419.41</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7135,14 +7135,14 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2022NE0002309</t>
+          <t>2022NE0002311</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6071.67</v>
+        <v>5806.22</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2022NE0002311</t>
+          <t>2022NE0002309</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>5806.22</v>
+        <v>6071.67</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7195,19 +7195,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2022NE0002312</t>
+          <t>2022NE0002310</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5419.41</v>
+        <v>10244.16</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7225,19 +7225,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2017NE01588</t>
+          <t>2017NE01587</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>6065</v>
+        <v>663.66</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7255,19 +7255,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
+          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2017NE01587</t>
+          <t>2017NE01588</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>663.66</v>
+        <v>6065</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7285,19 +7285,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
+          <t>1º TERMO ADITIVO AO CONTRATO 013/2015. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2016 A 28/09/20</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021NE0001197</t>
+          <t>2021NE0001198</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>7093.14</v>
+        <v>1937.82</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7315,19 +7315,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO 040/2020. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 24/11/2020 A 23/11/2021. VALOR GLOBAL: R$ 85.117,68. VALOR MENSAL: R$ 7.093,14. FUNDAMENTO LEGAL: ART</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021NE0001198</t>
+          <t>2021NE0001197</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1937.82</v>
+        <v>7093.14</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON. VIGÊNCIA: 08/10/2020 A 07/10/2021. VALOR GLOBAL: R$ 20.409</t>
+          <t>TERMO DE CONTRATO 040/2020. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 24/11/2020 A 23/11/2021. VALOR GLOBAL: R$ 85.117,68. VALOR MENSAL: R$ 7.093,14. FUNDAMENTO LEGAL: ART</t>
         </is>
       </c>
     </row>
@@ -7408,10 +7408,14 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2020NE00343</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
+          <t>2020NE00346</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr">
         <is>
           <t>12/03/2020</t>
@@ -7427,19 +7431,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>[ANULAÇÃO: EQUÍVOCO NO DESCRITIVO DO CONTRATO Nº 013/2015 - 01/12/2019-31/12/2019 - 2020NE00342]</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 13/2015. VIGÊNCIA: 29/09/2019 A 28/09/2020. SERVIÇOS DE ACESSO À INTERNET. PERÍODO: 01/12/2019 A 31/12/2019. 2020RD00172</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2020NE00342</t>
+          <t>2020NE00344</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7448,7 +7452,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>6467.5</v>
+        <v>1700.79</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7457,19 +7461,19 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 13/2015. VIGÊNCIA: 29/09/2019 A 28/09/2020. SERVIÇOS DE ACESSO À INTERNET. PERÍODO: 01/12/2019 A 31/12/2019. 2020RD00172</t>
+          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE LICENÇA DE USO MODELO 1, NO PERÍODO DE DEZEMBRO DE 2019, CONFORME CONTRATO Nº18/2019. COMPETÊNCIA 12/2019. VIGÊNCIA: 08/10/2019 A 07/10/2020. 2020RD00</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2020NE00344</t>
+          <t>2020NE00342</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7478,7 +7482,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1700.79</v>
+        <v>6467.5</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7487,21 +7491,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEBSITE LICENÇA DE USO MODELO 1, NO PERÍODO DE DEZEMBRO DE 2019, CONFORME CONTRATO Nº18/2019. COMPETÊNCIA 12/2019. VIGÊNCIA: 08/10/2019 A 07/10/2020. 2020RD00</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 13/2015. VIGÊNCIA: 29/09/2019 A 28/09/2020. SERVIÇOS DE ACESSO À INTERNET. PERÍODO: 01/12/2019 A 31/12/2019. 2020RD00172</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2020NE00346</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2020NE00343</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
           <t>12/03/2020</t>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 13/2015. VIGÊNCIA: 29/09/2019 A 28/09/2020. SERVIÇOS DE ACESSO À INTERNET. PERÍODO: 01/12/2019 A 31/12/2019. 2020RD00172</t>
+          <t>[ANULAÇÃO: EQUÍVOCO NO DESCRITIVO DO CONTRATO Nº 013/2015 - 01/12/2019-31/12/2019 - 2020NE00342]</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021NE0002160</t>
+          <t>2021NE0002161</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>511.73</v>
+        <v>3107.4</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7580,21 +7580,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021NE0002159</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>40/2020</t>
-        </is>
-      </c>
+          <t>2021NE0002157</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>11/11/2021</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>613.27</v>
+        <v>3395.14</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7640,17 +7636,21 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021NE0002157</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
+          <t>2021NE0002159</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>40/2020</t>
+        </is>
+      </c>
       <c r="C240" t="inlineStr">
         <is>
           <t>11/11/2021</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>3395.14</v>
+        <v>613.27</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021NE0002161</t>
+          <t>2021NE0002160</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3107.4</v>
+        <v>511.73</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7696,14 +7696,10 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2023NE01369</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>18/2019</t>
-        </is>
-      </c>
+          <t>2023NE0001369</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>11/08/2023</t>
@@ -7719,17 +7715,21 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 (DOZE) MESES E REAJUSTE pelo INPC 9,016730%. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFO</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2023NE0001369</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
+          <t>2023NE01369</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>18/2019</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
           <t>11/08/2023</t>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 018/2019. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 (DOZE) MESES E REAJUSTE pelo INPC 9,016730%. OBJETO DO CONTRATO: SERVIÇOS ESPECIALIZADOS EM REFO</t>
         </is>
       </c>
     </row>
@@ -7902,10 +7902,14 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2016NE02917</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>2016NE02918</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C249" t="inlineStr">
         <is>
           <t>10/10/2016</t>
@@ -7921,21 +7925,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 2491. MOTIVO: AJUSTE DE FONTE.</t>
+          <t xml:space="preserve">CONTRATO N.º 013/2015, EXTRATO PUBLICADO DO DOE DE 01/10/2015. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2015 A 28/09/2016. VALOR GLOBAL: R$ 72.780,00. VALOR MENSAL </t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2016NE02918</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2016NE02917</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
           <t>10/10/2016</t>
@@ -7951,17 +7951,21 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATO N.º 013/2015, EXTRATO PUBLICADO DO DOE DE 01/10/2015. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2015 A 28/09/2016. VALOR GLOBAL: R$ 72.780,00. VALOR MENSAL </t>
+          <t>ANULAÇÃO PARCIAL DA NE 2491. MOTIVO: AJUSTE DE FONTE.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2016NE02917</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
+          <t>2016NE02918</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C251" t="inlineStr">
         <is>
           <t>10/10/2016</t>
@@ -7977,21 +7981,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 2491. MOTIVO: AJUSTE DE FONTE.</t>
+          <t xml:space="preserve">CONTRATO N.º 013/2015, EXTRATO PUBLICADO DO DOE DE 01/10/2015. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2015 A 28/09/2016. VALOR GLOBAL: R$ 72.780,00. VALOR MENSAL </t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2016NE02918</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2016NE02917</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
           <t>10/10/2016</t>
@@ -8007,19 +8007,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATO N.º 013/2015, EXTRATO PUBLICADO DO DOE DE 01/10/2015. OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. VIGÊNCIA: 28/09/2015 A 28/09/2016. VALOR GLOBAL: R$ 72.780,00. VALOR MENSAL </t>
+          <t>ANULAÇÃO PARCIAL DA NE 2491. MOTIVO: AJUSTE DE FONTE.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2020NE01637</t>
+          <t>2020NE01636</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1329.98</v>
+        <v>11496.59</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8037,19 +8037,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE COMPLEMENTO MARÇO (R$ 447,44) E PARCIAL ABRIL (R$ 882,54).</t>
+          <t>FORNECIMENTO DE 01(UM) LINK DE INTERNET. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAÇÃO DE REAJUSTE DE 6,52%. COMPLEMENTO PARCELA JULHO (R$ 2.770,81), PARCELA AGOSTO (</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2020NE01636</t>
+          <t>2020NE01637</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>11496.59</v>
+        <v>1329.98</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 01(UM) LINK DE INTERNET. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAÇÃO DE REAJUSTE DE 6,52%. COMPLEMENTO PARCELA JULHO (R$ 2.770,81), PARCELA AGOSTO (</t>
+          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE COMPLEMENTO MARÇO (R$ 447,44) E PARCIAL ABRIL (R$ 882,54).</t>
         </is>
       </c>
     </row>
@@ -8104,12 +8104,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2022NE0001430</t>
+          <t>2022NE0001431</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3401.58</v>
+        <v>13221.96</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8127,19 +8127,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
+          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2022NE0001431</t>
+          <t>2022NE0001430</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>13221.96</v>
+        <v>3401.58</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VE</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITE DA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTI</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2015NE01318</t>
+          <t>2015NE01253</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 841/2015. MOTIVO: EQUIVOCO NO VALOR EMPENHADO</t>
+          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2015NE01253</t>
+          <t>2015NE01318</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
+          <t>ANULAÇÃO PARCIAL DA NE 841/2015. MOTIVO: EQUIVOCO NO VALOR EMPENHADO</t>
         </is>
       </c>
     </row>
@@ -8464,12 +8464,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025NE0000420</t>
+          <t>2025NE0000419</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>7567</v>
+        <v>19559.4</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8524,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025NE0000419</t>
+          <t>2025NE0000420</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>19559.4</v>
+        <v>7567</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2020NE02001</t>
+          <t>2020NE01997</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>6467.5</v>
+        <v>6071.65</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE NOVEMBRO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
+          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE JULHO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2020NE01998</t>
+          <t>2020NE02000</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>6071.65</v>
+        <v>6467.5</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE AGOSTO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
+          <t>SERVIÇOS DE FORNECIMENTO DE INTERNET NO PERÍODO DE OUTUBRO DE 2019, CONFORME 4º TERMO ADITIVO AO CONTRATO Nº 13/2015, VIGÊNCIA 29/09/2019 A 28/09/2020.</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2020NE02000</t>
+          <t>2020NE01998</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>6467.5</v>
+        <v>6071.65</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8723,14 +8723,14 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE FORNECIMENTO DE INTERNET NO PERÍODO DE OUTUBRO DE 2019, CONFORME 4º TERMO ADITIVO AO CONTRATO Nº 13/2015, VIGÊNCIA 29/09/2019 A 28/09/2020.</t>
+          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE AGOSTO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2020NE01997</t>
+          <t>2020NE02001</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6071.65</v>
+        <v>6467.5</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE JULHO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
+          <t>SERVIÇOS DE ACESSO À INTERNET NO PERÍODO DE NOVEMBRO DE 2019, CONFORME 3º TERMO ADITIVO AO CONTRATO Nº 13/2015.</t>
         </is>
       </c>
     </row>
@@ -8786,12 +8786,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026NE0000517</t>
+          <t>2026NE0000515</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>22/2025</t>
+          <t>25/2025</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
         </is>
       </c>
     </row>
@@ -8846,12 +8846,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026NE0000515</t>
+          <t>2026NE0000517</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>25/2025</t>
+          <t>22/2025</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026NE0000413</t>
+          <t>2026NE0000412</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026NE0000412</t>
+          <t>2026NE0000413</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8966,12 +8966,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026NE0000100</t>
+          <t>2026NE0000101</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>26/2025</t>
+          <t>25/2025</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>19559.4</v>
+        <v>7567</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8989,19 +8989,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
+          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026NE0000101</t>
+          <t>2026NE0000100</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>25/2025</t>
+          <t>26/2025</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>7567</v>
+        <v>19559.4</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CONTRATACAO DE PESSOA JURIDICA SERVIÇO DE ACESSO A INTERNET POR FIBRA ÓPTICA COM GARANTIA DE 100% EM DOWNLOAD E UPLOAD E CIRCUITO DE TRANSMISSÃO DE DADOS PARA CONEXÃO CLIENTE/FORNECEDOR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9082,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025NE0001677</t>
+          <t>2025NE0001676</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>19559.4</v>
+        <v>1878.01</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
@@ -9142,12 +9142,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025NE0001676</t>
+          <t>2025NE0001677</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1878.01</v>
+        <v>19559.4</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9165,28 +9165,24 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2018NE00855</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2018NE00845</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>598.49</v>
+        <v>663.66</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9195,17 +9191,21 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
+          <t>ANULAÇÃO PARCIAL DA NE 2018NE00819 REFERENTE A COMPETÊNCIA DO MÊS DE ABRIL/2018 MOTIVO: AJUSTE ORÇAMENTÁRIO.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2018NE00854</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
+          <t>2018NE00852</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C293" t="inlineStr">
         <is>
           <t>04/06/2018</t>
@@ -9221,21 +9221,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 2018NE00852, MOTIVO: DESCRIÇÃO INCORRETA.</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2018NE00852</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2018NE00854</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
           <t>04/06/2018</t>
@@ -9251,24 +9247,28 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
+          <t>ANULAÇÃO TOTAL DA NE 2018NE00852, MOTIVO: DESCRIÇÃO INCORRETA.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2018NE00845</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr"/>
+          <t>2018NE00855</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C295" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>663.66</v>
+        <v>598.49</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 2018NE00819 REFERENTE A COMPETÊNCIA DO MÊS DE ABRIL/2018 MOTIVO: AJUSTE ORÇAMENTÁRIO.</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025NE0003733</t>
+          <t>2025NE0003731</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>3239.86</v>
+        <v>17313.21</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9344,12 +9344,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025NE0003729</t>
+          <t>2025NE0003732</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>3749.31</v>
+        <v>3239.86</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 Vigência: 12/2023 à 12/2024.</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025NE0003732</t>
+          <t>2025NE0003729</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>3239.86</v>
+        <v>3749.31</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -9427,14 +9427,14 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 Vigência: 12/2023 à 12/2024.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025NE0003731</t>
+          <t>2025NE0003733</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>17313.21</v>
+        <v>3239.86</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2015NE01500</t>
+          <t>2015NE01498</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>898.2</v>
+        <v>662.66</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9487,19 +9487,19 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
+          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: AJUSTE ORÇAMENTÁRIO.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2015NE01501</t>
+          <t>2015NE01502</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>18/2011</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>8.34</v>
+        <v>1265.8</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 841/2015. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
+          <t xml:space="preserve">REF. AO 1º TERMO ADITIVO AO CONTRATO Nº 14/2014 DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO WEB SITE - VIGENCIA 04/06/2015 A 04/06/2016 NO VALOR MENSAL R$ 632,90 E VALOR GLOBAL </t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2015NE01502</t>
+          <t>2015NE01501</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>18/2011</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1265.8</v>
+        <v>8.34</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9577,14 +9577,14 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">REF. AO 1º TERMO ADITIVO AO CONTRATO Nº 14/2014 DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REFORMULAÇÃO E ATUALIZAÇÃO WEB SITE - VIGENCIA 04/06/2015 A 04/06/2016 NO VALOR MENSAL R$ 632,90 E VALOR GLOBAL </t>
+          <t>ANULAÇÃO DA NE 841/2015. MOTIVO: AJUSTE ORÇAMENTÁRIO</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2015NE01498</t>
+          <t>2015NE01500</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>662.66</v>
+        <v>898.2</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9607,19 +9607,19 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: AJUSTE ORÇAMENTÁRIO.</t>
+          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2024NE0001366</t>
+          <t>2024NE0001365</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>7567</v>
+        <v>2047.34</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024NE0001365</t>
+          <t>2024NE0001366</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2047.34</v>
+        <v>7567</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9697,19 +9697,19 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026NE0000400</t>
+          <t>2026NE0000405</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>5591.82</v>
+        <v>21677.63</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -9727,19 +9727,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026NE0000402</t>
+          <t>2026NE0000398</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5591.82</v>
+        <v>2047.34</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -9757,19 +9757,19 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t xml:space="preserve">CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O </t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026NE0000409</t>
+          <t>2026NE0000404</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>26/2025</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>21677.63</v>
+        <v>50328.89</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9787,19 +9787,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026NE0000399</t>
+          <t>2026NE0000408</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2047.34</v>
+        <v>21677.63</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9817,14 +9817,14 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O </t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026NE0000406</t>
+          <t>2026NE0000407</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9854,12 +9854,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026NE0000403</t>
+          <t>2026NE0000397</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>26/2025</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>4287.06</v>
+        <v>2717.66</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9877,19 +9877,19 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026NE0000410</t>
+          <t>2026NE0000401</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>21677.63</v>
+        <v>5591.82</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026NE0000401</t>
+          <t>2026NE0000410</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>5591.82</v>
+        <v>21677.63</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9967,19 +9967,19 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026NE0000397</t>
+          <t>2026NE0000403</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>26/2025</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2717.66</v>
+        <v>4287.06</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -9997,14 +9997,14 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM PARA WEBSITE</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026NE0000407</t>
+          <t>2026NE0000406</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10034,12 +10034,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026NE0000408</t>
+          <t>2026NE0000399</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>21677.63</v>
+        <v>2047.34</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10057,19 +10057,19 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
+          <t xml:space="preserve">CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O </t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026NE0000404</t>
+          <t>2026NE0000409</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>26/2025</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>50328.89</v>
+        <v>21677.63</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10087,19 +10087,19 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR OS SERVIDORES A SEREM UTILIZADOS NOS EQUIPAMENTOS DE RADIOTERAPIA</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026NE0000398</t>
+          <t>2026NE0000402</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2047.34</v>
+        <v>5591.82</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10117,19 +10117,19 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO, TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O </t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026NE0000405</t>
+          <t>2026NE0000400</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>21677.63</v>
+        <v>5591.82</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10147,19 +10147,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA. TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2019NE03208</t>
+          <t>2019NE03207</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1316.74</v>
+        <v>646.75</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10177,19 +10177,19 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE (OUT)</t>
+          <t>OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. (SET)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2019NE03207</t>
+          <t>2019NE03208</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>646.75</v>
+        <v>1316.74</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. (SET)</t>
+          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE (OUT)</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2025NE0000027</t>
+          <t>2025NE0000026</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18/2023</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>19559.4</v>
+        <v>1878.01</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10293,19 +10293,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2025NE0000026</t>
+          <t>2025NE0000027</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>18/2023</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10314,7 +10314,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1878.01</v>
+        <v>19559.4</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO PESSOA JURIDICA PARA SERVIÇOS DE HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA, TC: 0018/2023 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2023NE0000039</t>
+          <t>2023NE0000038</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>40/2020</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>7567</v>
+        <v>1878.01</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10383,19 +10383,19 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
+          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2023NE0000038</t>
+          <t>2023NE0000039</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>40/2020</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10404,7 +10404,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1878.01</v>
+        <v>7567</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10413,19 +10413,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>CONTRATAÇAO DE PESSOA JURIDICA PARA PRESTAÇÃO DE SERVIÇOS EM MANUTENÇÃO E SUPORTE DE REFORMULAÇÃO DO SITEDA FCECON, MELHORANDO O GERENCIAMENTO DE CONTEUDO , TOMANDO AS ATUALIZAÇÕES DE NOTICIAS SOBRE O</t>
+          <t>CONTRATAÇÃO DE PESSOA JURIDICA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE TELECOMUNICAÇÃO, OBJETIVANDO A IMPLANTAÇÃO, CONFIGURAÇÃO DE ACESSO À REDE INTERNET, POR INTERMEDIO DE 1 LINK DEDICADO COM VEL</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2020NE00013</t>
+          <t>2020NE00026</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>18/2019</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1700.79</v>
+        <v>12935</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10443,19 +10443,19 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE</t>
+          <t>OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAÇÃO DE REAJUSTE DE 6,52% SOBRE O VALOR DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2020NE00026</t>
+          <t>2020NE00013</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2019</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>12935</v>
+        <v>1700.79</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10473,19 +10473,19 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>OBJETO DO CONTRATO: FORNECIMENTO DE 01(UM) LINK DE INTERNET. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E APLICAÇÃO DE REAJUSTE DE 6,52% SOBRE O VALOR DO CONTRATO.</t>
+          <t>REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2019NE00040</t>
+          <t>2019NE00015</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10494,7 +10494,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1994.97</v>
+        <v>18214.95</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -10503,19 +10503,19 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
+          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2019NE00015</t>
+          <t>2019NE00040</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>18214.95</v>
+        <v>1994.97</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -10533,21 +10533,17 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2018NE00041</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2018NE00049</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
         <is>
           <t>02/01/2018</t>
@@ -10563,14 +10559,14 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
+          <t>ANULAÇÃO TOTAL DA NE 48. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2018NE00050</t>
+          <t>2018NE00048</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10600,21 +10596,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2018NE00042</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2018NE00047</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>663.66</v>
+        <v>6071.65</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10623,24 +10615,28 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
+          <t>ANULAÇÃO TOTAL DA NE 41. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2018NE00047</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr"/>
+          <t>2018NE00042</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C341" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>6071.65</v>
+        <v>663.66</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10649,14 +10645,14 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 41. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA FCECON.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2018NE00048</t>
+          <t>2018NE00050</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10686,10 +10682,14 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2018NE00049</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr"/>
+          <t>2018NE00041</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C343" t="inlineStr">
         <is>
           <t>02/01/2018</t>
@@ -10705,24 +10705,28 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 48. MOTIVO: EQUIVOCO NO DESCRITIVO</t>
+          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2017NE00070</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr"/>
+          <t>2017NE00067</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C344" t="inlineStr">
         <is>
           <t>02/01/2017</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>6065</v>
+        <v>632.9</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10731,14 +10735,14 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>EQUIVOCO NA CÉLULA ORÇAMENTÁRIA</t>
+          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2017NE00068</t>
+          <t>2017NE00072</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10768,7 +10772,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2017NE00072</t>
+          <t>2017NE00068</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10798,21 +10802,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2017NE00067</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+          <t>2017NE00070</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
           <t>02/01/2017</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>632.9</v>
+        <v>6065</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10821,19 +10821,19 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
+          <t>EQUIVOCO NA CÉLULA ORÇAMENTÁRIA</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2014NE00150</t>
+          <t>2014NE00154</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>18/2011</t>
+          <t>79/2009</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1500</v>
+        <v>87105.28</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10851,19 +10851,19 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Contrato No. 18/2011 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 79/2009 - Acesso Internet/Comput.banda 1,536Mb,c/Ass.-MetroMao</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2014NE00154</t>
+          <t>2014NE00150</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>79/2009</t>
+          <t>18/2011</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>87105.28</v>
+        <v>1500</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10881,14 +10881,14 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Contrato No. 79/2009 - Acesso Internet/Comput.banda 1,536Mb,c/Ass.-MetroMao</t>
+          <t>Contrato No. 18/2011 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2025NE0003190</t>
+          <t>2025NE0003191</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>7899.69</v>
+        <v>12653.18</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2025NE0003191</t>
+          <t>2025NE0003190</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>12653.18</v>
+        <v>7899.69</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2018NE00819</t>
+          <t>2018NE00780</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11154,7 +11154,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2018NE00818</t>
+          <t>2018NE00782</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1327.32</v>
+        <v>12143.34</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11173,21 +11173,17 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>anulação para correção da fundamentação legal.</t>
+          <t>ANULAÇÃO TOTAL PARA CORREÇÃO DA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2018NE00785</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>13/2015</t>
-        </is>
-      </c>
+          <t>2018NE00784</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr">
         <is>
           <t>01/06/2018</t>
@@ -11203,14 +11199,14 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 01 (UM) LINK DE INTERNET.</t>
+          <t>ANULAÇÃO PARA CORREÇÃO DA FUNDAMENTAÇÃO LEGAL.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2018NE00781</t>
+          <t>2018NE00783</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11240,7 +11236,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2018NE00783</t>
+          <t>2018NE00781</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11270,10 +11266,14 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2018NE00784</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr"/>
+          <t>2018NE00785</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>13/2015</t>
+        </is>
+      </c>
       <c r="C363" t="inlineStr">
         <is>
           <t>01/06/2018</t>
@@ -11289,14 +11289,14 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA CORREÇÃO DA FUNDAMENTAÇÃO LEGAL.</t>
+          <t>FORNECIMENTO DE 01 (UM) LINK DE INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2018NE00782</t>
+          <t>2018NE00818</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>12143.34</v>
+        <v>1327.32</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -11315,14 +11315,14 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA CORREÇÃO DA DESCRIÇÃO.</t>
+          <t>anulação para correção da fundamentação legal.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2018NE00780</t>
+          <t>2018NE00819</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11352,7 +11352,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2017NE00992</t>
+          <t>2017NE00991</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>597.29</v>
+        <v>63.29</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11375,14 +11375,14 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
+          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2017NE00991</t>
+          <t>2017NE00992</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11396,7 +11396,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>63.29</v>
+        <v>597.29</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO E IMPLANTAÇÃO E HOSPEDAGEM DE SITE DESTA </t>
+          <t>2º TERMO ADITIVO AO CONTRATO N.º 014/2014. OBJETO DO ADITIVO: PRORROGAR O PRAZO DE VIGÊNCIA PARA MAIS 12 MESES E REAJUSTAR O PREÇO DOS SERVIÇOS EM 4,86%. OBJETO DO CONTRATO: SERVIÇO DE DESENVOLVIMENTO</t>
         </is>
       </c>
     </row>
@@ -11472,12 +11472,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2016NE01145</t>
+          <t>2016NE01183</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>18/2011</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>6065</v>
+        <v>241.77</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11495,14 +11495,14 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>REFORÇO DA NOTA DE EMPENHO N.º 0992/2016 PARA ATENDER O CONT. N.º 013/2015 REF. A COMPETÊNCIA DE MARÇO DE 2016</t>
+          <t>6º T.A. CONT N.º 018/2011 - SERVIÇOS TÉCNICOS DE INFORMATICA DE FORMA EVENTUAIS - VIGÊNCIA: 12/04/2016 a 12/04/2017. - EMPENHO REFERENTE A COMPLEMENTO DO MÊS DE ABRIL DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2016NE01158</t>
+          <t>2016NE01147</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>139.97</v>
+        <v>449.1</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>5º T.A. CONT. N.º 015/2011 - SERVIÇOS TECNICOS EVENTUAIS DE INFORMATICA - VIGÊNCIA: 01/04/2016 a 12/04/2016</t>
+          <t>REFORÇO DA NOTA DE EMPENHO N.º 586/2016 - REFERENTE AO 4º T.A. CONT. N.º 18/2011 - REFERENTE A COMPETÊNCIA DE MARÇO DE 2016</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2016NE01147</t>
+          <t>2016NE01158</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>449.1</v>
+        <v>139.97</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11585,19 +11585,19 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>REFORÇO DA NOTA DE EMPENHO N.º 586/2016 - REFERENTE AO 4º T.A. CONT. N.º 18/2011 - REFERENTE A COMPETÊNCIA DE MARÇO DE 2016</t>
+          <t>5º T.A. CONT. N.º 015/2011 - SERVIÇOS TECNICOS EVENTUAIS DE INFORMATICA - VIGÊNCIA: 01/04/2016 a 12/04/2016</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2016NE01183</t>
+          <t>2016NE01145</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>18/2011</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>241.77</v>
+        <v>6065</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11615,14 +11615,14 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>6º T.A. CONT N.º 018/2011 - SERVIÇOS TÉCNICOS DE INFORMATICA DE FORMA EVENTUAIS - VIGÊNCIA: 12/04/2016 a 12/04/2017. - EMPENHO REFERENTE A COMPLEMENTO DO MÊS DE ABRIL DE 2016.</t>
+          <t>REFORÇO DA NOTA DE EMPENHO N.º 0992/2016 PARA ATENDER O CONT. N.º 013/2015 REF. A COMPETÊNCIA DE MARÇO DE 2016</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2015NE00661</t>
+          <t>2015NE00875</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>528.35</v>
+        <v>221.35</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2015NE00835</t>
+          <t>2015NE00838</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>528.35</v>
+        <v>269.45</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11675,14 +11675,14 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>REF. AO 3º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2014 A 12/04/2015 NO VALOR MENSAL R$ 528,35 E VALOR GLOBAL DE R$ 6.340,20</t>
+          <t>ANULAÇÃO TOTAL DA NE 836/2015. MOTIVO: EQUIVOCO NO PROCESSO</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2015NE00841</t>
+          <t>2015NE00836</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11705,14 +11705,14 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>cobertura do mes de abril 2015 - 4ºTA</t>
+          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2015NE00874</t>
+          <t>2015NE00869</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: EQUIVOCO NO VALOR EMPENHADO.</t>
+          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 01/04/2015 A 12/04/2015 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2015NE00869</t>
+          <t>2015NE00874</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11795,14 +11795,14 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 01/04/2015 A 12/04/2015 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
+          <t>ANULAÇÃO PARCIAL DA NE 117/2015. MOTIVO: EQUIVOCO NO VALOR EMPENHADO.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2015NE00836</t>
+          <t>2015NE00841</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11825,14 +11825,14 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>REF. AO 4º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2015 A 12/04/2016 NO VALOR MENSAL R$ 449,10 E VALOR GLOBAL DE R$ 5.389,20</t>
+          <t>cobertura do mes de abril 2015 - 4ºTA</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2015NE00838</t>
+          <t>2015NE00835</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>269.45</v>
+        <v>528.35</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11855,14 +11855,14 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 836/2015. MOTIVO: EQUIVOCO NO PROCESSO</t>
+          <t>REF. AO 3º TERMO ADITIVO AO CONTRATO Nº 18/2011 DE EMPRESA ESPECIALIZADA EM SERVIÇOS EVENTUAIS EM INFORMÁTICA - VIGENCIA 12/04/2014 A 12/04/2015 NO VALOR MENSAL R$ 528,35 E VALOR GLOBAL DE R$ 6.340,20</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2015NE00875</t>
+          <t>2015NE00661</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>221.35</v>
+        <v>528.35</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11918,12 +11918,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2016NE00663</t>
+          <t>2016NE00664</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>13/2015</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1265.8</v>
+        <v>12130</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇO DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON - REF. AO 1º TA AO CONTRATO 14/2014 - VIGENCIA: 04/06/2016 A 04/06/2016 - COMPETENCIA: JAN E FEV/2016</t>
+          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABAYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA - REF AO CONTRATO 13/2015 - VIGENCIA: 28/09/2015 A 28/09/2016 - COMPETENCIA: JAN E FEV/2016</t>
         </is>
       </c>
     </row>
@@ -11978,12 +11978,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2016NE00664</t>
+          <t>2016NE00663</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>13/2015</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>12130</v>
+        <v>1265.8</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>FORNECIMENTO DE 1(UM) LINK DE INTERNET DE 5MB/S (MEGABAYTE POR SEGUNDO) 7 DIAS POR SEMANA 24H POR DIA - REF AO CONTRATO 13/2015 - VIGENCIA: 28/09/2015 A 28/09/2016 - COMPETENCIA: JAN E FEV/2016</t>
+          <t>CONTRATAÇÃO DE SERVIÇO DE REFORMULAÇÃO E ATUALIZAÇÃO DE WEB SITE DESTA FCECON - REF. AO 1º TA AO CONTRATO 14/2014 - VIGENCIA: 04/06/2016 A 04/06/2016 - COMPETENCIA: JAN E FEV/2016</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/FCECON/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FCECON/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2029-08-31</t>
         </is>
       </c>
     </row>
